--- a/ascend_test_suite/v0.5.10-npu.rc1-910b/SGLang_model_list.xlsx
+++ b/ascend_test_suite/v0.5.10-npu.rc1-910b/SGLang_model_list.xlsx
@@ -1250,7 +1250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
     <col width="33.1818181818182" customWidth="1" style="2" min="1" max="1"/>
@@ -1481,12 +1481,34 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>docker run -itd --name sglang_mm --ipc=host --privileged --shm-size=10995116277 --workdir /workspace -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --device /dev/davinci_manager:/dev/davinci_manager --device /dev/devmm_svm:/dev/devmm_svm --device /dev/hisi_hdc:/dev/hisi_hdc -v /usr/local/Ascend/driver/lib64/:/usr/local/Ascend/driver/lib64/ -v /usr/local/Ascend/driver/include:/usr/local/Ascend/driver/include -v /usr/local/Ascend/driver/tools:/usr/local/Ascend/driver/tools -v /usr/local/Ascend/driver/version.info:/usr/local/Ascend/driver/version.info -v /etc/ascend_install.info:/etc/ascend_install.info -v /usr/local/dcmi:/usr/local/dcmi -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /usr/bin/hccn_tool:/usr/bin/hccn_tool -v /root/.cache:/root/.cache -v /data:/data -v /home/weight:/home/weight quay.io/ascend/sglang:v0.5.10-npu.rc1-910b python3 -m sglang.launch_server --model-path /home/weight/MiniMax-M2.5-w8a8-QuaRot --served-model-name MiniMax-M2.5-w8a8-QuaRot --port 4321 --tp-size 8 --host 0.0.0.0 --attention-backend ascend --device npu --trust-remote-code --mem-fraction-static 0.85 --tool-call-parser minimax-m2 --reasoning-parser minimax-append-think --quantization modelslim --disable-radix-cache</t>
+          <t>docker run -itd --name sglang_mm --ipc=host   --privileged   --shm-size=10995116277   --workdir /workspace   -v /dev/davinci0:/dev/davinci0   -v /dev/davinci1:/dev/davinci1   -v /dev/davinci2:/dev/davinci2   -v /dev/davinci3:/dev/davinci3   -v /dev/davinci4:/dev/davinci4   -v /dev/davinci5:/dev/davinci5   -v /dev/davinci6:/dev/davinci6   -v /dev/davinci7:/dev/davinci7   --device /dev/davinci_manager:/dev/davinci_manager   --device /dev/devmm_svm:/dev/devmm_svm   --device /dev/hisi_hdc:/dev/hisi_hdc   -v /usr/local/Ascend/driver/lib64/:/usr/local/Ascend/driver/lib64/   -v /usr/local/Ascend/driver/include:/usr/local/Ascend/driver/include   -v /usr/local/Ascend/driver/tools:/usr/local/Ascend/driver/tools    -v /usr/local/Ascend/driver/version.info:/usr/local/Ascend/driver/version.info   -v /etc/ascend_install.info:/etc/ascend_install.info   -v /usr/local/dcmi:/usr/local/dcmi   -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi   -v /usr/bin/hccn_tool:/usr/bin/hccn_tool   -v /root/.cache:/root/.cache   -v /data:/data   -v /home/weight:/home/weight   -v /root:/home/s_limingge  --workspace /home/s_limingge/sglang-universal-plugin  quay.io/ascend/sglang:cann9.0.0-910b-v0.5.16 PORT=30098 setsid bash scripts/run_minimax_tuned.sh --tp-size 8</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>QuaRot 可用 baseline: quay.io/ascend/sglang:v0.5.10-npu.rc1-910b（0.5.10rc1+npu）；v0.5.9 会报 Unsupported FusedMoe modelslim scheme: None / create_weights；8×910B；权重 Eco-Tech/MiniMax-M2.5-w8a8-QuaRot；需 --quantization modelslim</t>
+          <t>SGLang Pagoda / sglang-universal-plugin；--tp-size 8 供 CI 解析卡数，并传给 run_minimax_tuned.sh；端口通过 PORT 环境变量传入（Excel 示例 PORT=30098，CI 使用动态 $PORT）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MiniMax-M2.5-eagle3-sgl</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>910B</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>docker run -itd --name sglang_mm --ipc=host   --privileged   --shm-size=10995116277   --workdir /workspace   -v /dev/davinci0:/dev/davinci0   -v /dev/davinci1:/dev/davinci1   -v /dev/davinci2:/dev/davinci2   -v /dev/davinci3:/dev/davinci3   -v /dev/davinci4:/dev/davinci4   -v /dev/davinci5:/dev/davinci5   -v /dev/davinci6:/dev/davinci6   -v /dev/davinci7:/dev/davinci7   --device /dev/davinci_manager:/dev/davinci_manager   --device /dev/devmm_svm:/dev/devmm_svm   --device /dev/hisi_hdc:/dev/hisi_hdc   -v /usr/local/Ascend/driver/lib64/:/usr/local/Ascend/driver/lib64/   -v /usr/local/Ascend/driver/include:/usr/local/Ascend/driver/include   -v /usr/local/Ascend/driver/tools:/usr/local/Ascend/driver/tools    -v /usr/local/Ascend/driver/version.info:/usr/local/Ascend/driver/version.info   -v /etc/ascend_install.info:/etc/ascend_install.info   -v /usr/local/dcmi:/usr/local/dcmi   -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi   -v /usr/bin/hccn_tool:/usr/bin/hccn_tool   -v /root/.cache:/root/.cache   -v /data:/data   -v /home/weight:/home/weight   -v /root:/home/s_limingge  --workspace /home/s_limingge/sglang-universal-plugin  quay.io/ascend/sglang:cann9.0.0-910b-v0.5.16 DRAFT_PATH=/data/weight/MiniMax-M2.5-eagle3-sgl PORT=30098 setsid bash scripts/run_minimax_eagle3.sh --tp-size 8</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SGLang Pagoda / sglang-universal-plugin；DRAFT_PATH 指向 eagle3 draft 权重；--tp-size 8 仅供 CI 解析卡数（不传给 run_minimax_eagle3.sh）；端口通过 PORT 环境变量传入（Excel 示例 PORT=30098，CI 使用动态 $PORT）</t>
         </is>
       </c>
     </row>

--- a/ascend_test_suite/v0.5.10-npu.rc1-910b/SGLang_model_list.xlsx
+++ b/ascend_test_suite/v0.5.10-npu.rc1-910b/SGLang_model_list.xlsx
@@ -1481,34 +1481,34 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>docker run -itd --name sglang_mm --ipc=host   --privileged   --shm-size=10995116277   --workdir /workspace   -v /dev/davinci0:/dev/davinci0   -v /dev/davinci1:/dev/davinci1   -v /dev/davinci2:/dev/davinci2   -v /dev/davinci3:/dev/davinci3   -v /dev/davinci4:/dev/davinci4   -v /dev/davinci5:/dev/davinci5   -v /dev/davinci6:/dev/davinci6   -v /dev/davinci7:/dev/davinci7   --device /dev/davinci_manager:/dev/davinci_manager   --device /dev/devmm_svm:/dev/devmm_svm   --device /dev/hisi_hdc:/dev/hisi_hdc   -v /usr/local/Ascend/driver/lib64/:/usr/local/Ascend/driver/lib64/   -v /usr/local/Ascend/driver/include:/usr/local/Ascend/driver/include   -v /usr/local/Ascend/driver/tools:/usr/local/Ascend/driver/tools    -v /usr/local/Ascend/driver/version.info:/usr/local/Ascend/driver/version.info   -v /etc/ascend_install.info:/etc/ascend_install.info   -v /usr/local/dcmi:/usr/local/dcmi   -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi   -v /usr/bin/hccn_tool:/usr/bin/hccn_tool   -v /root/.cache:/root/.cache   -v /data:/data   -v /home/weight:/home/weight   -v /root:/home/s_limingge  --workspace /home/s_limingge/sglang-universal-plugin  quay.io/ascend/sglang:cann9.0.0-910b-v0.5.16 PORT=30098 setsid bash scripts/run_minimax_tuned.sh --tp-size 8</t>
+          <t>docker run -itd --name sglang_mm --ipc=host   --privileged   --shm-size=10995116277   --workdir /workspace   -v /dev/davinci0:/dev/davinci0   -v /dev/davinci1:/dev/davinci1   -v /dev/davinci2:/dev/davinci2   -v /dev/davinci3:/dev/davinci3   -v /dev/davinci4:/dev/davinci4   -v /dev/davinci5:/dev/davinci5   -v /dev/davinci6:/dev/davinci6   -v /dev/davinci7:/dev/davinci7   --device /dev/davinci_manager:/dev/davinci_manager   --device /dev/devmm_svm:/dev/devmm_svm   --device /dev/hisi_hdc:/dev/hisi_hdc   -v /usr/local/Ascend/driver/lib64/:/usr/local/Ascend/driver/lib64/   -v /usr/local/Ascend/driver/include:/usr/local/Ascend/driver/include   -v /usr/local/Ascend/driver/tools:/usr/local/Ascend/driver/tools    -v /usr/local/Ascend/driver/version.info:/usr/local/Ascend/driver/version.info   -v /etc/ascend_install.info:/etc/ascend_install.info   -v /usr/local/dcmi:/usr/local/dcmi   -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi   -v /usr/bin/hccn_tool:/usr/bin/hccn_tool   -v /root/.cache:/root/.cache   -v /data:/data   -v /home/weight:/home/weight   -v /root:/home/s_limingge  --workspace /home/s_limingge/sglang-universal-plugin  quay.io/ascend/sglang:cann9.0.0-910b-v0.5.16 bash -c "python3 -m sglang.launch_server --model-path /home/weights/MiniMax-M2.5-w8a8-QuaRot --device npu --tp-size 8 --mem-fraction-static 0.66 --max-running-requests 240 --host 0.0.0.0 --port 30098"</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>SGLang Pagoda / sglang-universal-plugin；--tp-size 8 供 CI 解析卡数，并传给 run_minimax_tuned.sh；端口通过 PORT 环境变量传入（Excel 示例 PORT=30098，CI 使用动态 $PORT）</t>
+          <t>标准 sglang.launch_server 启动；--tp-size 8 供 CI 解析卡数；Excel 示例端口 30098，CI 使用动态 $PORT；含 --mem-fraction-static 0.66 --max-running-requests 240</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>MiniMax-M2.5-eagle3-sgl</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>910B</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>docker run -itd --name sglang_mm --ipc=host   --privileged   --shm-size=10995116277   --workdir /workspace   -v /dev/davinci0:/dev/davinci0   -v /dev/davinci1:/dev/davinci1   -v /dev/davinci2:/dev/davinci2   -v /dev/davinci3:/dev/davinci3   -v /dev/davinci4:/dev/davinci4   -v /dev/davinci5:/dev/davinci5   -v /dev/davinci6:/dev/davinci6   -v /dev/davinci7:/dev/davinci7   --device /dev/davinci_manager:/dev/davinci_manager   --device /dev/devmm_svm:/dev/devmm_svm   --device /dev/hisi_hdc:/dev/hisi_hdc   -v /usr/local/Ascend/driver/lib64/:/usr/local/Ascend/driver/lib64/   -v /usr/local/Ascend/driver/include:/usr/local/Ascend/driver/include   -v /usr/local/Ascend/driver/tools:/usr/local/Ascend/driver/tools    -v /usr/local/Ascend/driver/version.info:/usr/local/Ascend/driver/version.info   -v /etc/ascend_install.info:/etc/ascend_install.info   -v /usr/local/dcmi:/usr/local/dcmi   -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi   -v /usr/bin/hccn_tool:/usr/bin/hccn_tool   -v /root/.cache:/root/.cache   -v /data:/data   -v /home/weight:/home/weight   -v /root:/home/s_limingge  --workspace /home/s_limingge/sglang-universal-plugin  quay.io/ascend/sglang:cann9.0.0-910b-v0.5.16 DRAFT_PATH=/data/weight/MiniMax-M2.5-eagle3-sgl PORT=30098 setsid bash scripts/run_minimax_eagle3.sh --tp-size 8</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SGLang Pagoda / sglang-universal-plugin；DRAFT_PATH 指向 eagle3 draft 权重；--tp-size 8 仅供 CI 解析卡数（不传给 run_minimax_eagle3.sh）；端口通过 PORT 环境变量传入（Excel 示例 PORT=30098，CI 使用动态 $PORT）</t>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>docker run -itd --name sglang_mm --ipc=host   --privileged   --shm-size=10995116277   --workdir /workspace   -v /dev/davinci0:/dev/davinci0   -v /dev/davinci1:/dev/davinci1   -v /dev/davinci2:/dev/davinci2   -v /dev/davinci3:/dev/davinci3   -v /dev/davinci4:/dev/davinci4   -v /dev/davinci5:/dev/davinci5   -v /dev/davinci6:/dev/davinci6   -v /dev/davinci7:/dev/davinci7   --device /dev/davinci_manager:/dev/davinci_manager   --device /dev/devmm_svm:/dev/devmm_svm   --device /dev/hisi_hdc:/dev/hisi_hdc   -v /usr/local/Ascend/driver/lib64/:/usr/local/Ascend/driver/lib64/   -v /usr/local/Ascend/driver/include:/usr/local/Ascend/driver/include   -v /usr/local/Ascend/driver/tools:/usr/local/Ascend/driver/tools    -v /usr/local/Ascend/driver/version.info:/usr/local/Ascend/driver/version.info   -v /etc/ascend_install.info:/etc/ascend_install.info   -v /usr/local/dcmi:/usr/local/dcmi   -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi   -v /usr/bin/hccn_tool:/usr/bin/hccn_tool   -v /root/.cache:/root/.cache   -v /data:/data   -v /home/weight:/home/weight   -v /root:/home/s_limingge  --workspace /home/s_limingge/sglang-universal-plugin  quay.io/ascend/sglang:cann9.0.0-910b-v0.5.16 bash -c "cd /work/sglang-pagoda &amp;&amp; SGLANG_M2_ATTN_SCATTER=4 TOK_WORKERS=4 PORT=30098 bash ./scripts/run_minimax_scatter.sh --tp-size 8"</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>SGLang Pagoda；容器内 cd /work/sglang-pagoda 后执行 SGLANG_M2_ATTN_SCATTER=4 PORT=30098 ./run_minimax_plain.sh --tp-size 8；端口以 PORT 环境变量传入（Excel 示例 30098，CI 使用动态 $PORT）；--tp-size 8 供 CI 解析卡数</t>
         </is>
       </c>
     </row>
